--- a/practo_test.xlsx
+++ b/practo_test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\308298\Desktop\Testing Notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50B68C8A-5D00-42D4-BC2E-9AFB13D349F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AC1F42C-FC51-4DCF-A89B-AB1D626DA418}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{08BC8C98-BD9B-4318-BCD3-5E87805AC0E0}"/>
   </bookViews>
@@ -306,9 +306,6 @@
     <t>TC_Practo_12</t>
   </si>
   <si>
-    <t>To verify whether the location choosing option is visible.</t>
-  </si>
-  <si>
     <t>1. Open browser 2. Enter URL 3. Observe location dropdown</t>
   </si>
   <si>
@@ -349,6 +346,9 @@
   </si>
   <si>
     <t>"Add to cart" button should be visible</t>
+  </si>
+  <si>
+    <t>vs</t>
   </si>
 </sst>
 </file>
@@ -1086,7 +1086,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="58" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>17</v>
       </c>
@@ -1405,7 +1405,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>83</v>
       </c>
@@ -1416,19 +1416,19 @@
         <v>28</v>
       </c>
       <c r="D13" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>39</v>
       </c>
       <c r="G13" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H13" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>87</v>
       </c>
       <c r="I13" s="6" t="s">
         <v>29</v>
@@ -1436,7 +1436,7 @@
     </row>
     <row r="14" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>10</v>
@@ -1445,19 +1445,19 @@
         <v>28</v>
       </c>
       <c r="D14" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>90</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>39</v>
       </c>
       <c r="G14" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="H14" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>92</v>
       </c>
       <c r="I14" s="6" t="s">
         <v>29</v>
@@ -1465,7 +1465,7 @@
     </row>
     <row r="15" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>10</v>
@@ -1474,19 +1474,19 @@
         <v>28</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>39</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>29</v>
@@ -1494,7 +1494,7 @@
     </row>
     <row r="16" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>10</v>
@@ -1503,19 +1503,19 @@
         <v>28</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>39</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I16" s="6" t="s">
         <v>29</v>
@@ -1540,5 +1540,6 @@
     <hyperlink ref="F16" r:id="rId15" display="https://www.practo.com/tests" xr:uid="{3E389A98-81B0-443D-8362-2DEAB8D26F2A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId16"/>
 </worksheet>
 </file>